--- a/sources/table_normalization/xlsx/employment-table21.xlsx
+++ b/sources/table_normalization/xlsx/employment-table21.xlsx
@@ -115,7 +115,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -134,6 +134,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -147,7 +153,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -155,6 +161,7 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -829,13 +836,13 @@
       <c r="D19">
         <v>38.5</v>
       </c>
-      <c r="E19" t="s">
+      <c r="E19" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="F19" t="s">
+      <c r="F19" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="G19" t="s">
+      <c r="G19" s="5" t="s">
         <v>21</v>
       </c>
     </row>
@@ -852,13 +859,13 @@
       <c r="D20">
         <v>41.9</v>
       </c>
-      <c r="E20" t="s">
+      <c r="E20" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="F20" t="s">
+      <c r="F20" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="G20" t="s">
+      <c r="G20" s="5" t="s">
         <v>21</v>
       </c>
     </row>
